--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487407_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487407_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3177</v>
+        <v>5.947</v>
       </c>
       <c r="E2" t="n">
-        <v>4.236</v>
+        <v>3.9455</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0817</v>
+        <v>2.0015</v>
       </c>
       <c r="G2" t="n">
         <v>3.1556</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6529</v>
+        <v>0.2822</v>
       </c>
       <c r="T2" t="n">
-        <v>0.414</v>
+        <v>0.1235</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2388</v>
+        <v>0.1587</v>
       </c>
       <c r="V2" t="n">
         <v>0.5507</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7951</v>
+        <v>4.7653</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7359</v>
+        <v>3.2407</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0593</v>
+        <v>1.5247</v>
       </c>
       <c r="G3" t="n">
         <v>5.2537</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0451</v>
+        <v>0.0153</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3546</v>
+        <v>-0.1406</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6905</v>
+        <v>0.1559</v>
       </c>
       <c r="V3" t="n">
         <v>-1.483</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1759</v>
+        <v>3.1656</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4285</v>
+        <v>1.445</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7474</v>
+        <v>1.7207</v>
       </c>
       <c r="G4" t="n">
         <v>1.0787</v>
@@ -766,13 +766,13 @@
         <v>0.9792</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8426</v>
+        <v>0.8324</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2358</v>
+        <v>0.2523</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6068</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0.2754</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5506</v>
+        <v>2.4821</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7799</v>
+        <v>2.2736</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7707</v>
+        <v>0.2084</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0181</v>
+        <v>2.0992</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0731</v>
+        <v>3.9486</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0912</v>
+        <v>-1.8495</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3097</v>
+        <v>2.8159</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7487</v>
+        <v>3.6049</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.789</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2916</v>
+        <v>-0.7167</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8218</v>
+        <v>0.3437</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5302</v>
+        <v>-1.0604</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9585</v>
+        <v>0.9792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9377</v>
+        <v>-0.1958</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7023</v>
+        <v>-0.663</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2024</v>
+        <v>-0.3464</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4999</v>
+        <v>-0.3166</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8249</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8249</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7087</v>
+        <v>1.4549</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8478</v>
+        <v>0.9171</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1391</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0992</v>
+        <v>1.8988</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9486</v>
+        <v>1.5751</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8495</v>
+        <v>0.3237</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8159</v>
+        <v>1.2041</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6049</v>
+        <v>1.1637</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.789</v>
+        <v>0.0404</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7167</v>
+        <v>0.6947</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3437</v>
+        <v>0.4114</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0604</v>
+        <v>0.2833</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9792</v>
+        <v>1.5668</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4363</v>
+        <v>-0.9182</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7722</v>
+        <v>-0.287</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6641</v>
+        <v>-0.6312</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06660000000000001</v>
+        <v>-1.0924</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06660000000000001</v>
+        <v>-1.0924</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9073</v>
+        <v>0.9721</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6101</v>
+        <v>-0.3888</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2973</v>
+        <v>1.3608</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8988</v>
+        <v>-0.3483</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5751</v>
+        <v>1.5772</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3237</v>
+        <v>-1.9255</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2041</v>
+        <v>-0.6399</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1637</v>
+        <v>0.7554</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0404</v>
+        <v>-1.3952</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6947</v>
+        <v>0.2916</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4114</v>
+        <v>0.8218</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2833</v>
+        <v>-0.5302</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4658</v>
+        <v>0.3411</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.594</v>
+        <v>0.2511</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8718</v>
+        <v>0.09</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0924</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4968</v>
+        <v>0.6526</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9418</v>
+        <v>-0.8395</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4386</v>
+        <v>1.4921</v>
       </c>
       <c r="G8" t="n">
         <v>0.9741</v>
@@ -1078,13 +1078,13 @@
         <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.202</v>
+        <v>-0.0462</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.594</v>
+        <v>-0.4917</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3921</v>
+        <v>0.4455</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2754</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. REGUERA SOUTO</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0499</v>
+        <v>0.4356</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-1.148</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0499</v>
+        <v>1.5836</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2052</v>
+        <v>-1.0181</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0677</v>
+        <v>0.0731</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2729</v>
+        <v>-1.0912</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-1.3097</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.7487</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2052</v>
+        <v>0.2916</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0677</v>
+        <v>0.8218</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2729</v>
+        <v>-0.5302</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2551</v>
+        <v>1.5872</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.2745</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2551</v>
+        <v>0.3127</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.8249</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8249</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>R. REGUERA SOUTO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3839</v>
+        <v>-0.0232</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5309</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.147</v>
+        <v>-0.0232</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3483</v>
+        <v>0.2052</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5772</v>
+        <v>-0.0677</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9255</v>
+        <v>0.2729</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6399</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7554</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3952</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2916</v>
+        <v>0.2052</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8218</v>
+        <v>-0.0677</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5302</v>
+        <v>0.2729</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0149</v>
+        <v>-0.2283</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.891</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1239</v>
+        <v>-0.2283</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3617</v>
+        <v>-0.516</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8675</v>
+        <v>-2.0753</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5059</v>
+        <v>1.5593</v>
       </c>
       <c r="G11" t="n">
         <v>0.576</v>
@@ -1312,13 +1312,13 @@
         <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5343</v>
+        <v>0.3114</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3276</v>
+        <v>0.4646</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2067</v>
+        <v>-0.1532</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2076</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4525</v>
+        <v>-1.135</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5695</v>
+        <v>-0.3054</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.883</v>
+        <v>-0.8295</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3381</v>
@@ -1390,13 +1390,13 @@
         <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1395</v>
+        <v>-0.8219</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3564</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.783</v>
+        <v>-0.7296</v>
       </c>
       <c r="V12" t="n">
         <v>-1.15</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7051</v>
+        <v>-2.0139</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7726</v>
+        <v>-3.921</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0675</v>
+        <v>1.9071</v>
       </c>
       <c r="G13" t="n">
         <v>-3.9908</v>
@@ -1468,13 +1468,13 @@
         <v>1.5668</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1901</v>
+        <v>0.8813</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6246</v>
+        <v>0.227</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8147</v>
+        <v>0.6543</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2754</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.999</v>
+        <v>16.1871</v>
       </c>
       <c r="E14" t="n">
-        <v>1.955899999999999</v>
+        <v>3.143900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>13.0434</v>
+        <v>13.0433</v>
       </c>
       <c r="G14" t="n">
-        <v>9.545999999999999</v>
+        <v>9.545999999999998</v>
       </c>
       <c r="H14" t="n">
         <v>17.0247</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.478599999999998</v>
+        <v>-7.4786</v>
       </c>
       <c r="J14" t="n">
         <v>6.2658</v>
@@ -1525,7 +1525,7 @@
         <v>10.515</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.249000000000001</v>
+        <v>-4.249</v>
       </c>
       <c r="M14" t="n">
         <v>3.2805</v>
@@ -1546,13 +1546,13 @@
         <v>15.6677</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3851000000000007</v>
+        <v>1.5733</v>
       </c>
       <c r="T14" t="n">
-        <v>0.04700000000000037</v>
+        <v>1.235</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3381999999999999</v>
+        <v>0.3382999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-2.7662</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8299</v>
+        <v>0.0593</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.451</v>
+        <v>-1.5533</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2809</v>
+        <v>1.6127</v>
       </c>
       <c r="G15" t="n">
         <v>-1.4157</v>
@@ -1624,13 +1624,13 @@
         <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9417</v>
+        <v>1.1711</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1941</v>
+        <v>0.0917</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7477</v>
+        <v>1.0794</v>
       </c>
       <c r="V15" t="n">
         <v>1.2832</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ALVAREZ HERNAN</t>
+          <t>A. HARRIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5907</v>
+        <v>-0.9197</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4807</v>
+        <v>-1.4178</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.11</v>
+        <v>0.4981</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8146</v>
+        <v>-1.1213</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9136</v>
+        <v>-3.5918</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7282</v>
+        <v>2.4705</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4001</v>
+        <v>-0.3441</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0345</v>
+        <v>-2.1013</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4345</v>
+        <v>1.7571</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5854</v>
+        <v>-0.7771</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8791</v>
+        <v>-1.4905</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2937</v>
+        <v>0.7134</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3709</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.101</v>
+        <v>-0.4274</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0018</v>
+        <v>-0.1359</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0992</v>
+        <v>-0.2916</v>
       </c>
       <c r="V16" t="n">
-        <v>0.06660000000000001</v>
+        <v>1.2166</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. HARRIS</t>
+          <t>M. ALVAREZ HERNAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4184</v>
+        <v>-1.178</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6224</v>
+        <v>-1.0947</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2041</v>
+        <v>-0.0833</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1213</v>
+        <v>0.8146</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.5918</v>
+        <v>-1.9136</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4705</v>
+        <v>2.7282</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3441</v>
+        <v>1.4001</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.1013</v>
+        <v>-1.0345</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7571</v>
+        <v>2.4345</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7771</v>
+        <v>-0.5854</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4905</v>
+        <v>-0.8791</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7134</v>
+        <v>0.2937</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5875</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9261</v>
+        <v>-0.6883</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3405</v>
+        <v>-0.6158</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5856</v>
+        <v>-0.0725</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2166</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2088</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7165</v>
+        <v>-1.4721</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1364</v>
+        <v>-1.6247</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4199</v>
+        <v>0.1526</v>
       </c>
       <c r="G18" t="n">
         <v>1.1646</v>
@@ -1858,13 +1858,13 @@
         <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7946</v>
+        <v>-0.5502</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0998</v>
+        <v>-0.5881</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3053</v>
+        <v>0.0379</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3239</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. VARELA BARRAL</t>
+          <t>G. PREOTU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7174</v>
+        <v>-1.8907</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3836</v>
+        <v>-0.8703</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6662</v>
+        <v>-1.0205</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7745</v>
+        <v>-3.5069</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3355</v>
+        <v>-3.5628</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3797</v>
+        <v>-2.5183</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3845</v>
+        <v>-2.0025</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0048</v>
+        <v>-0.5158</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3948</v>
+        <v>-0.9886</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.951</v>
+        <v>-1.5603</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5562</v>
+        <v>0.5717</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.1336</v>
+        <v>0.1958</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.1128</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6412</v>
+        <v>-0.1958</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2841</v>
+        <v>0.1941</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3571</v>
+        <v>-0.3899</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5495</v>
+        <v>1.6161</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8249</v>
+        <v>2.4332</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2754</v>
+        <v>-0.8171</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. PREOTU</t>
+          <t>R. VARELA BARRAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3184</v>
+        <v>-1.9801</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8703</v>
+        <v>-2.4859</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4482</v>
+        <v>0.5058</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.5069</v>
+        <v>-0.7745</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.5628</v>
+        <v>-1.3355</v>
       </c>
       <c r="I20" t="n">
-        <v>0.056</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5183</v>
+        <v>-0.3797</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.0025</v>
+        <v>-0.3845</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5158</v>
+        <v>0.0048</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9886</v>
+        <v>-0.3948</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5603</v>
+        <v>-0.951</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5717</v>
+        <v>0.5562</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1958</v>
+        <v>-3.1336</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>-4.1128</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.3785</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1941</v>
+        <v>0.1817</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8176</v>
+        <v>0.1967</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6161</v>
+        <v>1.5495</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4332</v>
+        <v>1.8249</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8171</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1309</v>
+        <v>-2.9751</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9184</v>
+        <v>-0.8161</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2125</v>
+        <v>-2.159</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8912</v>
@@ -2092,13 +2092,13 @@
         <v>0.1958</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9436</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.297</v>
+        <v>-0.1947</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6466</v>
+        <v>-0.5931</v>
       </c>
       <c r="V21" t="n">
         <v>-1.492</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9367</v>
+        <v>-4.6427</v>
       </c>
       <c r="E22" t="n">
         <v>-3.1805</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7562</v>
+        <v>-1.4622</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8157</v>
@@ -2170,13 +2170,13 @@
         <v>0.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4207</v>
+        <v>0.7147</v>
       </c>
       <c r="T22" t="n">
         <v>0.7287</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.308</v>
+        <v>-0.014</v>
       </c>
       <c r="V22" t="n">
         <v>-1.15</v>
@@ -2209,7 +2209,7 @@
         <v>-13.0433</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9558</v>
+        <v>-1.955799999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-9.546099999999999</v>
@@ -2218,7 +2218,7 @@
         <v>-17.0247</v>
       </c>
       <c r="I23" t="n">
-        <v>7.4786</v>
+        <v>7.478599999999999</v>
       </c>
       <c r="J23" t="n">
         <v>-3.280200000000001</v>
@@ -2248,13 +2248,13 @@
         <v>7.8338</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3851999999999999</v>
+        <v>-0.3852000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3381000000000002</v>
+        <v>-0.3382999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.04689999999999972</v>
+        <v>-0.04710000000000014</v>
       </c>
       <c r="V23" t="n">
         <v>2.7661</v>
